--- a/healthcare_forms/018_medical_excuse_note_request--healthcare_forms.xlsx
+++ b/healthcare_forms/018_medical_excuse_note_request--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'general_practitioner',_'value':_'general_practitioner'}</t>
+          <t>general_practitioner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'General Practitioner', 'value': 'General Practitioner'}</t>
+          <t>General Practitioner</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'specialist',_'value':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Specialist', 'value': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'acute',_'value':_'acute'}</t>
+          <t>acute</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Acute', 'value': 'Acute'}</t>
+          <t>Acute</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'chronic',_'value':_'chronic'}</t>
+          <t>chronic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Chronic', 'value': 'Chronic'}</t>
+          <t>Chronic</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'another_option_1',_'value':_'another_option_1'}</t>
+          <t>another_option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Another option 1', 'value': 'Another option 1'}</t>
+          <t>Another option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'another_option_2',_'value':_'another_option_2'}</t>
+          <t>another_option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Another option 2', 'value': 'Another option 2'}</t>
+          <t>Another option 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'another_option_3',_'value':_'another_option_3'}</t>
+          <t>another_option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Another option 3', 'value': 'Another option 3'}</t>
+          <t>Another option 3</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'another_option',_'value':_'another_option'}</t>
+          <t>another_option</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Another option', 'value': 'Another option'}</t>
+          <t>Another option</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'another_option_2',_'value':_'another_option_2'}</t>
+          <t>another_option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Another option 2', 'value': 'Another option 2'}</t>
+          <t>Another option 2</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'another_option_3',_'value':_'another_option_3'}</t>
+          <t>another_option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Another option 3', 'value': 'Another option 3'}</t>
+          <t>Another option 3</t>
         </is>
       </c>
     </row>
